--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkail\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFA836C1-3CEF-4BA8-A8C6-614041D47381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F238A0-5349-43F3-8942-950742B66F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
   <si>
     <t>Category</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Beef cows</t>
+  </si>
+  <si>
+    <t>Sustainable Factor</t>
   </si>
 </sst>
 </file>
@@ -512,15 +515,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:D31"/>
+  <dimension ref="B3:E31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="32.26953125" customWidth="1"/>
-    <col min="3" max="3" width="29.36328125" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="3" max="4" width="29.36328125" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,54 +531,69 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
         <v>47894500</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4">
         <v>858000</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="5">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="5">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
@@ -583,10 +601,13 @@
         <v>9</v>
       </c>
       <c r="D8" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="E8" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
@@ -594,32 +615,41 @@
         <v>10</v>
       </c>
       <c r="D9" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="E9" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="5">
+        <v>14.1</v>
+      </c>
+      <c r="E10" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D11" s="5">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E11" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -627,10 +657,13 @@
         <v>13</v>
       </c>
       <c r="D12" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="E12" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
@@ -638,32 +671,41 @@
         <v>14</v>
       </c>
       <c r="D13" s="2">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="E14" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="5">
+        <v>25.6</v>
+      </c>
+      <c r="E15" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
@@ -671,10 +713,13 @@
         <v>17</v>
       </c>
       <c r="D16" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="E16" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
@@ -682,32 +727,41 @@
         <v>18</v>
       </c>
       <c r="D17" s="2">
+        <v>30.2</v>
+      </c>
+      <c r="E17" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="5">
+        <v>32.5</v>
+      </c>
+      <c r="E18" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="5">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E19" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -715,10 +769,13 @@
         <v>23</v>
       </c>
       <c r="D20" s="2">
+        <v>37.1</v>
+      </c>
+      <c r="E20" s="2">
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
@@ -726,32 +783,41 @@
         <v>24</v>
       </c>
       <c r="D21" s="2">
+        <v>39.4</v>
+      </c>
+      <c r="E21" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="5">
+        <v>41.7</v>
+      </c>
+      <c r="E22" s="2">
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="5">
+        <v>44</v>
+      </c>
+      <c r="E23" s="2">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
@@ -759,10 +825,13 @@
         <v>27</v>
       </c>
       <c r="D24" s="2">
+        <v>46.3</v>
+      </c>
+      <c r="E24" s="2">
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
         <v>22</v>
       </c>
@@ -770,32 +839,41 @@
         <v>28</v>
       </c>
       <c r="D25" s="2">
+        <v>48.6</v>
+      </c>
+      <c r="E25" s="2">
         <v>239</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="5">
+        <v>50.9</v>
+      </c>
+      <c r="E26" s="2">
         <v>240</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="5">
+        <v>53.2</v>
+      </c>
+      <c r="E27" s="2">
         <v>241</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
@@ -803,10 +881,13 @@
         <v>31</v>
       </c>
       <c r="D28" s="2">
+        <v>55.5</v>
+      </c>
+      <c r="E28" s="2">
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>22</v>
       </c>
@@ -814,28 +895,37 @@
         <v>32</v>
       </c>
       <c r="D29" s="2">
+        <v>57.8</v>
+      </c>
+      <c r="E29" s="2">
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="5">
+        <v>60.1</v>
+      </c>
+      <c r="E30" s="2">
         <v>244</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="5">
+        <v>62.4</v>
+      </c>
+      <c r="E31" s="2">
         <v>245</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkail\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F238A0-5349-43F3-8942-950742B66F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C4ECA3-452D-4DEB-AD58-0AA59A157708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-9690" yWindow="-2700" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>Category</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Sustainable Factor</t>
+  </si>
+  <si>
+    <t>Sustainable Potential</t>
   </si>
 </sst>
 </file>
@@ -515,15 +518,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E31"/>
+  <dimension ref="B3:F31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="32.26953125" customWidth="1"/>
-    <col min="3" max="4" width="29.36328125" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="3" max="5" width="29.36328125" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,10 +537,13 @@
         <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
@@ -547,11 +553,14 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
+        <v>23</v>
+      </c>
+      <c r="F4" s="3">
         <v>47894500</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
@@ -561,11 +570,14 @@
       <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4">
         <v>858000</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
@@ -575,11 +587,14 @@
       <c r="D6" s="5">
         <v>4</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="5">
+        <v>234</v>
+      </c>
+      <c r="F6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
@@ -590,10 +605,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="2">
+        <v>308</v>
+      </c>
+      <c r="F7" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
@@ -604,10 +622,13 @@
         <v>9.5</v>
       </c>
       <c r="E8" s="2">
+        <v>413.5</v>
+      </c>
+      <c r="F8" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
@@ -617,11 +638,14 @@
       <c r="D9" s="2">
         <v>11.8</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="5">
+        <v>519</v>
+      </c>
+      <c r="F9" s="2">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
@@ -632,10 +656,13 @@
         <v>14.1</v>
       </c>
       <c r="E10" s="2">
+        <v>624.5</v>
+      </c>
+      <c r="F10" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -646,10 +673,13 @@
         <v>16.399999999999999</v>
       </c>
       <c r="E11" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+        <v>730</v>
+      </c>
+      <c r="F11" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
@@ -659,11 +689,14 @@
       <c r="D12" s="2">
         <v>18.7</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="5">
+        <v>835.5</v>
+      </c>
+      <c r="F12" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
@@ -674,10 +707,13 @@
         <v>21</v>
       </c>
       <c r="E13" s="2">
+        <v>941</v>
+      </c>
+      <c r="F13" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
@@ -688,10 +724,13 @@
         <v>23.3</v>
       </c>
       <c r="E14" s="2">
+        <v>1046.5</v>
+      </c>
+      <c r="F14" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
@@ -701,11 +740,14 @@
       <c r="D15" s="5">
         <v>25.6</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="5">
+        <v>1152</v>
+      </c>
+      <c r="F15" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
@@ -716,10 +758,13 @@
         <v>27.9</v>
       </c>
       <c r="E16" s="2">
+        <v>1257.5</v>
+      </c>
+      <c r="F16" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
@@ -730,10 +775,13 @@
         <v>30.2</v>
       </c>
       <c r="E17" s="2">
+        <v>1363</v>
+      </c>
+      <c r="F17" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
@@ -743,11 +791,14 @@
       <c r="D18" s="5">
         <v>32.5</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="5">
+        <v>1468.5</v>
+      </c>
+      <c r="F18" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
@@ -758,10 +809,13 @@
         <v>34.799999999999997</v>
       </c>
       <c r="E19" s="2">
+        <v>1574</v>
+      </c>
+      <c r="F19" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -772,10 +826,13 @@
         <v>37.1</v>
       </c>
       <c r="E20" s="2">
+        <v>1679.5</v>
+      </c>
+      <c r="F20" s="2">
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
@@ -786,10 +843,13 @@
         <v>39.4</v>
       </c>
       <c r="E21" s="2">
+        <v>1785</v>
+      </c>
+      <c r="F21" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
@@ -800,10 +860,13 @@
         <v>41.7</v>
       </c>
       <c r="E22" s="2">
+        <v>1890.5</v>
+      </c>
+      <c r="F22" s="2">
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
@@ -813,11 +876,14 @@
       <c r="D23" s="5">
         <v>44</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="5">
+        <v>1996</v>
+      </c>
+      <c r="F23" s="2">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
@@ -828,10 +894,13 @@
         <v>46.3</v>
       </c>
       <c r="E24" s="2">
+        <v>2101.5</v>
+      </c>
+      <c r="F24" s="2">
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
         <v>22</v>
       </c>
@@ -842,10 +911,13 @@
         <v>48.6</v>
       </c>
       <c r="E25" s="2">
+        <v>2207</v>
+      </c>
+      <c r="F25" s="2">
         <v>239</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
         <v>22</v>
       </c>
@@ -855,11 +927,14 @@
       <c r="D26" s="5">
         <v>50.9</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="5">
+        <v>2312.5</v>
+      </c>
+      <c r="F26" s="2">
         <v>240</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
@@ -870,10 +945,13 @@
         <v>53.2</v>
       </c>
       <c r="E27" s="2">
+        <v>2418</v>
+      </c>
+      <c r="F27" s="2">
         <v>241</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
@@ -884,10 +962,13 @@
         <v>55.5</v>
       </c>
       <c r="E28" s="2">
+        <v>2523.5</v>
+      </c>
+      <c r="F28" s="2">
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>22</v>
       </c>
@@ -897,11 +978,14 @@
       <c r="D29" s="2">
         <v>57.8</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="5">
+        <v>2629</v>
+      </c>
+      <c r="F29" s="2">
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
@@ -912,10 +996,13 @@
         <v>60.1</v>
       </c>
       <c r="E30" s="2">
+        <v>2734.5</v>
+      </c>
+      <c r="F30" s="2">
         <v>244</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
@@ -926,6 +1013,9 @@
         <v>62.4</v>
       </c>
       <c r="E31" s="2">
+        <v>2840</v>
+      </c>
+      <c r="F31" s="2">
         <v>245</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkail\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C4ECA3-452D-4DEB-AD58-0AA59A157708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C6F85E-DD74-414C-839E-4BF786AA15BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9690" yWindow="-2700" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="890" yWindow="840" windowWidth="15280" windowHeight="9790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
   <si>
     <t>Category</t>
   </si>
@@ -141,12 +141,6 @@
   </si>
   <si>
     <t>Beef cows</t>
-  </si>
-  <si>
-    <t>Sustainable Factor</t>
-  </si>
-  <si>
-    <t>Sustainable Potential</t>
   </si>
 </sst>
 </file>
@@ -518,15 +512,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:F31"/>
+  <dimension ref="B3:D31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="32.26953125" customWidth="1"/>
-    <col min="3" max="5" width="29.36328125" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="3" max="3" width="29.36328125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,220 +528,142 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3">
-        <v>47894500</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D4" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2">
-        <v>34</v>
-      </c>
-      <c r="F5" s="4">
-        <v>858000</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D5" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="5">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5">
-        <v>234</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D6" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2">
-        <v>308</v>
-      </c>
-      <c r="F7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D7" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="E8" s="2">
-        <v>413.5</v>
-      </c>
-      <c r="F8" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D8" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="2">
-        <v>11.8</v>
-      </c>
-      <c r="E9" s="5">
-        <v>519</v>
-      </c>
-      <c r="F9" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D9" s="4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="5">
-        <v>14.1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>624.5</v>
-      </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D10" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="5">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="E11" s="2">
-        <v>730</v>
-      </c>
-      <c r="F11" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D11" s="4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="2">
-        <v>18.7</v>
-      </c>
-      <c r="E12" s="5">
-        <v>835.5</v>
-      </c>
-      <c r="F12" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D12" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="2">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2">
-        <v>941</v>
-      </c>
-      <c r="F13" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D13" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="5">
-        <v>23.3</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1046.5</v>
-      </c>
-      <c r="F14" s="2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="D14" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="5">
-        <v>25.6</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1152</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="D15" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
@@ -755,16 +671,10 @@
         <v>17</v>
       </c>
       <c r="D16" s="2">
-        <v>27.9</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1257.5</v>
-      </c>
-      <c r="F16" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
@@ -772,50 +682,32 @@
         <v>18</v>
       </c>
       <c r="D17" s="2">
-        <v>30.2</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1363</v>
-      </c>
-      <c r="F17" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="5">
-        <v>32.5</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1468.5</v>
-      </c>
-      <c r="F18" s="2">
+      <c r="D18" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="5">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1574</v>
-      </c>
-      <c r="F19" s="2">
+      <c r="D19" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="s">
         <v>22</v>
       </c>
@@ -823,16 +715,10 @@
         <v>23</v>
       </c>
       <c r="D20" s="2">
-        <v>37.1</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1679.5</v>
-      </c>
-      <c r="F20" s="2">
         <v>234</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
@@ -840,50 +726,32 @@
         <v>24</v>
       </c>
       <c r="D21" s="2">
-        <v>39.4</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1785</v>
-      </c>
-      <c r="F21" s="2">
         <v>235</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="5">
-        <v>41.7</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1890.5</v>
-      </c>
-      <c r="F22" s="2">
+      <c r="D22" s="2">
         <v>236</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="5">
-        <v>44</v>
-      </c>
-      <c r="E23" s="5">
-        <v>1996</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="D23" s="2">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
@@ -891,16 +759,10 @@
         <v>27</v>
       </c>
       <c r="D24" s="2">
-        <v>46.3</v>
-      </c>
-      <c r="E24" s="2">
-        <v>2101.5</v>
-      </c>
-      <c r="F24" s="2">
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
         <v>22</v>
       </c>
@@ -908,50 +770,32 @@
         <v>28</v>
       </c>
       <c r="D25" s="2">
-        <v>48.6</v>
-      </c>
-      <c r="E25" s="2">
-        <v>2207</v>
-      </c>
-      <c r="F25" s="2">
         <v>239</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="5">
-        <v>50.9</v>
-      </c>
-      <c r="E26" s="5">
-        <v>2312.5</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="D26" s="2">
         <v>240</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="5">
-        <v>53.2</v>
-      </c>
-      <c r="E27" s="2">
-        <v>2418</v>
-      </c>
-      <c r="F27" s="2">
+      <c r="D27" s="2">
         <v>241</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>22</v>
       </c>
@@ -959,16 +803,10 @@
         <v>31</v>
       </c>
       <c r="D28" s="2">
-        <v>55.5</v>
-      </c>
-      <c r="E28" s="2">
-        <v>2523.5</v>
-      </c>
-      <c r="F28" s="2">
         <v>242</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>22</v>
       </c>
@@ -976,46 +814,28 @@
         <v>32</v>
       </c>
       <c r="D29" s="2">
-        <v>57.8</v>
-      </c>
-      <c r="E29" s="5">
-        <v>2629</v>
-      </c>
-      <c r="F29" s="2">
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="5">
-        <v>60.1</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2734.5</v>
-      </c>
-      <c r="F30" s="2">
+      <c r="D30" s="2">
         <v>244</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="5">
-        <v>62.4</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2840</v>
-      </c>
-      <c r="F31" s="2">
+      <c r="D31" s="2">
         <v>245</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkail\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C6F85E-DD74-414C-839E-4BF786AA15BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6C78B5-BFC6-4688-9265-5A044BFC4FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="890" yWindow="840" windowWidth="15280" windowHeight="9790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="45">
   <si>
     <t>Category</t>
   </si>
@@ -47,9 +48,6 @@
     <t>Production Volume</t>
   </si>
   <si>
-    <t>Forestry</t>
-  </si>
-  <si>
     <t>Softwood Lumber</t>
   </si>
   <si>
@@ -74,27 +72,6 @@
     <t>Corn</t>
   </si>
   <si>
-    <t>oats</t>
-  </si>
-  <si>
-    <t>soybean</t>
-  </si>
-  <si>
-    <t>rye</t>
-  </si>
-  <si>
-    <t>dry beans</t>
-  </si>
-  <si>
-    <t>flaxseed</t>
-  </si>
-  <si>
-    <t>dry peas</t>
-  </si>
-  <si>
-    <t>mustard seed</t>
-  </si>
-  <si>
     <t>Urban Waste</t>
   </si>
   <si>
@@ -141,6 +118,60 @@
   </si>
   <si>
     <t>Beef cows</t>
+  </si>
+  <si>
+    <t>Forestry Biomass</t>
+  </si>
+  <si>
+    <t>Oats</t>
+  </si>
+  <si>
+    <t>Soybean</t>
+  </si>
+  <si>
+    <t>Rye</t>
+  </si>
+  <si>
+    <t>Dry Beans</t>
+  </si>
+  <si>
+    <t>Flaxseed</t>
+  </si>
+  <si>
+    <t>Dry Peas</t>
+  </si>
+  <si>
+    <t>Mustard Seed</t>
+  </si>
+  <si>
+    <t>ALBERTA</t>
+  </si>
+  <si>
+    <t>residue</t>
+  </si>
+  <si>
+    <t>sf</t>
+  </si>
+  <si>
+    <t>46.02-71.98</t>
+  </si>
+  <si>
+    <t>46.02-71.99</t>
+  </si>
+  <si>
+    <t>thousand tonnes</t>
+  </si>
+  <si>
+    <t>Crop Residue</t>
+  </si>
+  <si>
+    <t>BRITISH COLUMBIA</t>
+  </si>
+  <si>
+    <t>Forestry Biomass Residue</t>
+  </si>
+  <si>
+    <t>88.35</t>
   </si>
 </sst>
 </file>
@@ -150,7 +181,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +201,12 @@
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -192,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -215,22 +252,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -511,16 +581,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:D31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1041260-7941-47D9-AF17-6677D4F48067}">
+  <dimension ref="B1:H45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="32.26953125" customWidth="1"/>
     <col min="3" max="3" width="29.36328125" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" customWidth="1"/>
+    <col min="7" max="7" width="1.90625" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,316 +609,1066 @@
       <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4">
+        <v>8971100</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6">
+        <v>5824.1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5">
+        <v>103.7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5">
+        <v>87.8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5">
+        <v>57.5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="D12" s="5">
+        <v>663.4</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5">
+        <v>58.9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="5">
+        <v>56.4</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15820.3478</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="5">
+        <v>5483.1149999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4226.7359999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5">
+        <v>395.03750000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="5">
+        <v>153.45000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="5">
+        <v>946.9559999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="5">
+        <v>154.7175</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="5">
+        <v>61.267999999999994</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="5">
+        <v>27.863999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1165.8330000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="5">
+        <v>49.192</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="D34" s="5">
+        <v>180500</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="5">
+        <v>6912864</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="5">
+        <v>1813730.0000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="5">
+        <v>5657280</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="5">
+        <v>1247232</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="D39" s="5">
+        <v>1825824</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="5">
+        <v>533082</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="5">
+        <v>6664.0000000000009</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="5">
+        <v>3893184</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="5">
+        <v>175440</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="4">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="4">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="2">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D44" s="5">
+        <v>1794518.9999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="2">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="2">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="2">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="2">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="2">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="2">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="2">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="2">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="2">
-        <v>245</v>
+      <c r="D45" s="5">
+        <v>19678848</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:G45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="32.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.36328125" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="15.453125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="1.90625" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>5824.1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7">
+        <v>11717819.380000001</v>
+      </c>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="7">
+        <v>9921.7000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="7">
+        <v>10206.68</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="8">
+        <v>5483.1149999999998</v>
+      </c>
+      <c r="E9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="9">
+        <v>4226.7359999999999</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="8">
+        <v>316.03000000000003</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="9">
+        <v>153.45000000000002</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="8">
+        <v>631.30399999999997</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8">
+        <v>88.41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="9">
+        <v>72.08</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="10">
+        <v>23.22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="10">
+        <v>1165.8330000000001</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="10">
+        <v>22.880000000000003</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="10">
+        <v>155.55000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="10">
+        <v>87.8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="10">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="10">
+        <v>663.4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="10">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="10"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" s="10">
+        <v>37810</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="10">
+        <v>732240</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="10">
+        <v>1822810</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="10">
+        <v>208320</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="10">
+        <v>190464</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="10">
+        <v>348384</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="10">
+        <v>553377</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="10">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="10">
+        <v>184032</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="10">
+        <v>11696</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="10">
+        <v>101393.99999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="10">
+        <v>2737728</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jkail\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6C78B5-BFC6-4688-9265-5A044BFC4FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9A5E4B-6FD4-45AD-9510-BFA28D04EDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -168,10 +168,10 @@
     <t>BRITISH COLUMBIA</t>
   </si>
   <si>
-    <t>Forestry Biomass Residue</t>
-  </si>
-  <si>
     <t>88.35</t>
+  </si>
+  <si>
+    <t>Forestry Residue</t>
   </si>
 </sst>
 </file>
@@ -655,7 +655,7 @@
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -1206,7 +1206,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -1446,7 +1446,7 @@
         <v>28</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.35">
